--- a/artfynd/A 62040-2024 artfynd.xlsx
+++ b/artfynd/A 62040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852561</v>
       </c>
       <c r="B2" t="n">
-        <v>97408</v>
+        <v>97415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62040-2024 artfynd.xlsx
+++ b/artfynd/A 62040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852561</v>
       </c>
       <c r="B2" t="n">
-        <v>97415</v>
+        <v>97416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62040-2024 artfynd.xlsx
+++ b/artfynd/A 62040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852561</v>
       </c>
       <c r="B2" t="n">
-        <v>97416</v>
+        <v>97418</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62040-2024 artfynd.xlsx
+++ b/artfynd/A 62040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852561</v>
       </c>
       <c r="B2" t="n">
-        <v>97418</v>
+        <v>97422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62040-2024 artfynd.xlsx
+++ b/artfynd/A 62040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852561</v>
       </c>
       <c r="B2" t="n">
-        <v>97422</v>
+        <v>97423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62040-2024 artfynd.xlsx
+++ b/artfynd/A 62040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852561</v>
       </c>
       <c r="B2" t="n">
-        <v>97423</v>
+        <v>97425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62040-2024 artfynd.xlsx
+++ b/artfynd/A 62040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852561</v>
       </c>
       <c r="B2" t="n">
-        <v>97425</v>
+        <v>97427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62040-2024 artfynd.xlsx
+++ b/artfynd/A 62040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852561</v>
       </c>
       <c r="B2" t="n">
-        <v>97427</v>
+        <v>97429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62040-2024 artfynd.xlsx
+++ b/artfynd/A 62040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852561</v>
       </c>
       <c r="B2" t="n">
-        <v>97429</v>
+        <v>97433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62040-2024 artfynd.xlsx
+++ b/artfynd/A 62040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852561</v>
       </c>
       <c r="B2" t="n">
-        <v>97433</v>
+        <v>97436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62040-2024 artfynd.xlsx
+++ b/artfynd/A 62040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852561</v>
       </c>
       <c r="B2" t="n">
-        <v>97436</v>
+        <v>97445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62040-2024 artfynd.xlsx
+++ b/artfynd/A 62040-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,6 +792,121 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128390916</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58532</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Äsperöd, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>322839</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6470601</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anna Lindstein</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anna Lindstein</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62040-2024 artfynd.xlsx
+++ b/artfynd/A 62040-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>128390916</v>
       </c>
       <c r="B3" t="n">
-        <v>58532</v>
+        <v>58544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62040-2024 artfynd.xlsx
+++ b/artfynd/A 62040-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>128390916</v>
       </c>
       <c r="B3" t="n">
-        <v>58544</v>
+        <v>58548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62040-2024 artfynd.xlsx
+++ b/artfynd/A 62040-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>128390916</v>
       </c>
       <c r="B3" t="n">
-        <v>58548</v>
+        <v>58575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
